--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T15:25:42+00:00</t>
+    <t>2023-05-11T15:26:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T15:26:02+00:00</t>
+    <t>2023-05-11T16:43:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:43:02+00:00</t>
+    <t>2023-05-11T16:43:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:43:55+00:00</t>
+    <t>2023-05-11T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:57:46+00:00</t>
+    <t>2023-05-11T16:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:58:30+00:00</t>
+    <t>2023-05-11T17:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T17:51:02+00:00</t>
+    <t>2023-05-11T17:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/transport-location</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/transport-location</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T17:51:30+00:00</t>
+    <t>2023-05-11T18:15:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:15:51+00:00</t>
+    <t>2023-05-11T18:16:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/transport-location</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/transport-location</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:16:31+00:00</t>
+    <t>2023-05-11T18:27:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:27:59+00:00</t>
+    <t>2023-05-11T18:29:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:29:46+00:00</t>
+    <t>2023-05-11T18:48:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:48:31+00:00</t>
+    <t>2023-05-11T18:54:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:54:41+00:00</t>
+    <t>2023-05-11T19:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:41:30+00:00</t>
+    <t>2023-05-11T19:42:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:42:15+00:00</t>
+    <t>2023-05-11T20:23:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:23:29+00:00</t>
+    <t>2023-05-11T20:24:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:24:51+00:00</t>
+    <t>2023-05-12T02:48:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T02:48:54+00:00</t>
+    <t>2023-05-12T02:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T02:49:37+00:00</t>
+    <t>2023-05-12T07:30:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:30:25+00:00</t>
+    <t>2023-05-12T07:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:30:35+00:00</t>
+    <t>2023-05-12T07:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:36:14+00:00</t>
+    <t>2023-05-12T07:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:36:30+00:00</t>
+    <t>2023-05-12T07:54:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:54:06+00:00</t>
+    <t>2023-05-12T07:55:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:55:51+00:00</t>
+    <t>2023-05-12T10:26:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:26:59+00:00</t>
+    <t>2023-05-12T10:27:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:27:50+00:00</t>
+    <t>2023-05-12T10:32:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:32:06+00:00</t>
+    <t>2023-05-12T10:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:40:31+00:00</t>
+    <t>2023-05-12T13:37:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:37:18+00:00</t>
+    <t>2023-05-12T13:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:51:30+00:00</t>
+    <t>2023-05-23T09:07:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-transport-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T09:07:38+00:00</t>
+    <t>2023-05-23T09:13:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
